--- a/pass and username.xlsx
+++ b/pass and username.xlsx
@@ -30,12 +30,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>IRJAN TORO</t>
   </si>
   <si>
     <t>B09263084</t>
+  </si>
+  <si>
+    <t>DIDI RIYADI</t>
+  </si>
+  <si>
+    <t>B09262985</t>
   </si>
 </sst>
 </file>
@@ -421,7 +427,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -453,6 +459,21 @@
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -581,7 +602,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,34 +614,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -705,11 +726,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1237,7 +1261,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultColWidth="13.89" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="32.04" style="1" customWidth="1"/>
@@ -1675,51 +1699,59 @@
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:2">
-      <c r="A44" s="2" t="str">
+      <c r="A44" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AHMAD MUZAKIR")</f>
         <v>AHMAD MUZAKIR</v>
       </c>
-      <c r="B44" s="2" t="str">
+      <c r="B44" s="3" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B09241103")</f>
         <v>B09241103</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:2">
-      <c r="A45" s="2" t="str">
+      <c r="A45" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HARUN NURASYID")</f>
         <v>HARUN NURASYID</v>
       </c>
-      <c r="B45" s="2" t="str">
+      <c r="B45" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B09241341")</f>
         <v>B09241341</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:2">
-      <c r="A46" s="2" t="str">
+      <c r="A46" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RIKO SETIADI")</f>
         <v>RIKO SETIADI</v>
       </c>
-      <c r="B46" s="2" t="str">
+      <c r="B46" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B09241104")</f>
         <v>B09241104</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:2">
-      <c r="A47" s="2" t="str">
+      <c r="A47" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRISNO SUSANTO")</f>
         <v>TRISNO SUSANTO</v>
       </c>
-      <c r="B47" s="2" t="str">
+      <c r="B47" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"B09241105")</f>
         <v>B09241105</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:2">
+      <c r="A49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
